--- a/OSP O365 License .xlsx
+++ b/OSP O365 License .xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\SLTSERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F01D0CF-7499-4362-A8E3-3D2B88964AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F888CE2-D4F2-4649-B0A3-6A0233FD32A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28F35E17-5A2C-4D9D-B5AC-2CE17E7AC0E7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="365" sheetId="1" r:id="rId1"/>
+    <sheet name="CAD" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'365'!$A$1:$J$160</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="754">
   <si>
     <t>No</t>
   </si>
@@ -2280,6 +2284,27 @@
   </si>
   <si>
     <t>2025-02-17 09:29:58Z</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>Delete After 2026-07-31</t>
+  </si>
+  <si>
+    <t>sadeep</t>
+  </si>
+  <si>
+    <t>Nuwan Sadeepa</t>
+  </si>
+  <si>
+    <t>User Replace</t>
+  </si>
+  <si>
+    <t>Need New Microsoft 365 Business Standard (no Teams)</t>
   </si>
 </sst>
 </file>
@@ -2311,12 +2336,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2332,10 +2369,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2671,10 +2711,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}">
-  <dimension ref="A1:I159"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="45.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2702,8 +2754,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2732,7 +2787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2761,7 +2816,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2790,36 +2845,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3">
         <v>679</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2845,7 +2903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2874,7 +2932,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2903,7 +2961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2932,7 +2990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2961,7 +3019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2990,7 +3048,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3019,7 +3077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3048,7 +3106,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3077,7 +3135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3106,7 +3164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3135,7 +3193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3164,7 +3222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3193,7 +3251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3222,7 +3280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3251,7 +3309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3280,7 +3338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3309,7 +3367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3338,7 +3396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3367,7 +3425,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3396,7 +3454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3425,36 +3483,37 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C27" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27">
+      <c r="G27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="4">
         <v>1322</v>
       </c>
-      <c r="I27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3483,7 +3542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3512,7 +3571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3541,7 +3600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3570,7 +3629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4524,36 +4583,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G65" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65">
+      <c r="G65" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" s="3">
         <v>1031</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65" s="3" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4582,7 +4644,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4611,7 +4673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4640,7 +4702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4669,7 +4731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4698,7 +4760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4727,7 +4789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4756,7 +4818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4785,7 +4847,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4814,7 +4876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4843,7 +4905,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4872,7 +4934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4901,7 +4963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4930,7 +4992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4959,7 +5021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5277,7 +5339,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" t="s">
         <v>433</v>
@@ -5306,7 +5368,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" t="s">
         <v>438</v>
@@ -5335,7 +5397,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" t="s">
         <v>443</v>
@@ -5364,7 +5426,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94" t="s">
         <v>448</v>
@@ -5393,7 +5455,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95" t="s">
         <v>453</v>
@@ -5422,7 +5484,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" t="s">
         <v>458</v>
@@ -5451,7 +5513,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" t="s">
         <v>463</v>
@@ -5480,7 +5542,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" t="s">
         <v>468</v>
@@ -5509,7 +5571,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" t="s">
         <v>473</v>
@@ -5538,7 +5600,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100" t="s">
         <v>478</v>
@@ -5567,7 +5629,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" t="s">
         <v>483</v>
@@ -5596,7 +5658,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" t="s">
         <v>488</v>
@@ -5625,7 +5687,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" t="s">
         <v>493</v>
@@ -5654,7 +5716,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" t="s">
         <v>497</v>
@@ -5683,7 +5745,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" t="s">
         <v>501</v>
@@ -5712,7 +5774,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106" t="s">
         <v>505</v>
@@ -5741,7 +5803,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" t="s">
         <v>509</v>
@@ -5770,7 +5832,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" t="s">
         <v>514</v>
@@ -5799,7 +5861,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" t="s">
         <v>518</v>
@@ -5828,7 +5890,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" t="s">
         <v>523</v>
@@ -5857,7 +5919,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" t="s">
         <v>527</v>
@@ -5886,7 +5948,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" t="s">
         <v>532</v>
@@ -5915,7 +5977,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B113" t="s">
         <v>536</v>
@@ -5944,7 +6006,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
         <v>541</v>
@@ -5973,7 +6035,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B115" t="s">
         <v>546</v>
@@ -6002,7 +6064,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B116" t="s">
         <v>550</v>
@@ -6031,7 +6093,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B117" t="s">
         <v>554</v>
@@ -6060,7 +6122,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B118" t="s">
         <v>559</v>
@@ -6089,7 +6151,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B119" t="s">
         <v>564</v>
@@ -6118,7 +6180,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B120" t="s">
         <v>569</v>
@@ -6147,7 +6209,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" t="s">
         <v>573</v>
@@ -6176,7 +6238,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122" t="s">
         <v>578</v>
@@ -6205,7 +6267,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" t="s">
         <v>581</v>
@@ -6234,7 +6296,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
         <v>586</v>
@@ -6263,7 +6325,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" t="s">
         <v>591</v>
@@ -6292,7 +6354,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" t="s">
         <v>596</v>
@@ -6321,7 +6383,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127" t="s">
         <v>600</v>
@@ -6350,7 +6412,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B128" t="s">
         <v>605</v>
@@ -6379,7 +6441,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B129" t="s">
         <v>610</v>
@@ -6408,7 +6470,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B130" t="s">
         <v>615</v>
@@ -6437,7 +6499,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B131" t="s">
         <v>617</v>
@@ -6466,7 +6528,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132" t="s">
         <v>622</v>
@@ -6495,7 +6557,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B133" t="s">
         <v>624</v>
@@ -6521,7 +6583,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B134" t="s">
         <v>629</v>
@@ -6550,7 +6612,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B135" t="s">
         <v>633</v>
@@ -6579,7 +6641,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B136" t="s">
         <v>637</v>
@@ -6608,7 +6670,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B137" t="s">
         <v>642</v>
@@ -6637,7 +6699,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B138" t="s">
         <v>647</v>
@@ -6666,7 +6728,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B139" t="s">
         <v>652</v>
@@ -6695,7 +6757,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B140" t="s">
         <v>657</v>
@@ -6724,7 +6786,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B141" t="s">
         <v>661</v>
@@ -6753,7 +6815,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B142" t="s">
         <v>665</v>
@@ -6782,7 +6844,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B143" t="s">
         <v>668</v>
@@ -6811,7 +6873,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B144" t="s">
         <v>673</v>
@@ -6838,9 +6900,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B145" t="s">
         <v>678</v>
@@ -6867,9 +6929,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B146" t="s">
         <v>683</v>
@@ -6896,9 +6958,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B147" t="s">
         <v>687</v>
@@ -6925,9 +6987,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B148" t="s">
         <v>692</v>
@@ -6954,9 +7016,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B149" t="s">
         <v>697</v>
@@ -6983,9 +7045,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B150" t="s">
         <v>702</v>
@@ -7012,9 +7074,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B151" t="s">
         <v>706</v>
@@ -7041,9 +7103,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B152" t="s">
         <v>711</v>
@@ -7070,9 +7132,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B153" t="s">
         <v>716</v>
@@ -7099,9 +7161,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B154" t="s">
         <v>720</v>
@@ -7128,9 +7190,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B155" t="s">
         <v>724</v>
@@ -7157,9 +7219,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B156" t="s">
         <v>729</v>
@@ -7186,9 +7248,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B157" t="s">
         <v>734</v>
@@ -7215,9 +7277,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B158" t="s">
         <v>738</v>
@@ -7244,9 +7306,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B159" t="s">
         <v>742</v>
@@ -7267,16 +7329,56 @@
         <v>14</v>
       </c>
       <c r="H159">
-        <v>7677</v>
+        <v>1691</v>
       </c>
       <c r="I159" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="160" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="4">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="F160" s="4"/>
+      <c r="G160" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H160" s="4">
+        <v>1825</v>
+      </c>
+      <c r="I160" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J160" s="4" t="s">
+        <v>752</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:J160" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}"/>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{EA8A47DA-5E75-4647-879D-B98C23F16FB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22829FDD-79DF-48F8-AE57-654453DB04ED}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/OSP O365 License .xlsx
+++ b/OSP O365 License .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\SLTSERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F888CE2-D4F2-4649-B0A3-6A0233FD32A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74726D33-F4C5-417C-9F86-4A1DC5CC736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28F35E17-5A2C-4D9D-B5AC-2CE17E7AC0E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{28F35E17-5A2C-4D9D-B5AC-2CE17E7AC0E7}"/>
   </bookViews>
   <sheets>
     <sheet name="365" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="767">
   <si>
     <t>No</t>
   </si>
@@ -2305,13 +2305,52 @@
   </si>
   <si>
     <t>Need New Microsoft 365 Business Standard (no Teams)</t>
+  </si>
+  <si>
+    <t>Need to Upgrade Microsoft 365 Business Standard (no Teams)</t>
+  </si>
+  <si>
+    <t>Emp  No </t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>I.  G. S. Nuwan Gunathunga</t>
+  </si>
+  <si>
+    <t>M.H.lakni shalika malwenna</t>
+  </si>
+  <si>
+    <t>A. H. M.D. Dananjaya Bandara</t>
+  </si>
+  <si>
+    <t>K.G.A.P.Wickramarathna</t>
+  </si>
+  <si>
+    <t>B.L.D. Kavinda</t>
+  </si>
+  <si>
+    <t>K.G.H.S.Tharaka</t>
+  </si>
+  <si>
+    <t>A. L. R. Kalogasthenna</t>
+  </si>
+  <si>
+    <t>D.K.N.B Delgahapela</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>R.W.M.P.G.M.R. Rajapaksha</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2329,14 +2368,21 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2355,6 +2401,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2369,13 +2421,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2711,54 +2769,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2788,35 +2848,38 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="4">
         <v>1805</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2845,46 +2908,46 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+    <row r="5" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2">
         <v>679</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
@@ -2903,7 +2966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2932,7 +2995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2961,7 +3024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2990,7 +3053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3019,7 +3082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3048,7 +3111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3077,7 +3140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3106,7 +3169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3135,7 +3198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3164,7 +3227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3193,7 +3256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3222,7 +3285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3251,7 +3314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3280,7 +3343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3309,7 +3372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3338,7 +3401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3367,7 +3430,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3396,7 +3459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3425,7 +3488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3454,7 +3517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3483,37 +3546,37 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+    <row r="27" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="G27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="3">
         <v>1322</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="4" t="s">
+      <c r="I27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3542,7 +3605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3571,7 +3634,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3600,7 +3663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3630,35 +3693,38 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32">
+      <c r="G32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="4">
         <v>7205</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3687,7 +3753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3716,7 +3782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3745,7 +3811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3774,7 +3840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3803,7 +3869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3832,7 +3898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3861,7 +3927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3890,7 +3956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3919,7 +3985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3948,7 +4014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3977,36 +4043,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="G44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44">
+      <c r="G44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="4">
         <v>1343</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4035,7 +4104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4064,7 +4133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4090,7 +4159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4119,7 +4188,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4148,7 +4217,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4177,7 +4246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4206,7 +4275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4235,7 +4304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4264,7 +4333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4293,7 +4362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4322,7 +4391,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4351,7 +4420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4380,7 +4449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4409,7 +4478,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4438,7 +4507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4467,36 +4536,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="G61" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61">
+      <c r="G61" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="4">
         <v>7481</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4525,36 +4597,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="G63" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63">
+      <c r="G63" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="4">
         <v>431</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J63" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4584,38 +4659,38 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" s="3">
+      <c r="G65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" s="2">
         <v>1031</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="2" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4644,7 +4719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4673,7 +4748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4703,35 +4778,38 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="G69" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69">
+      <c r="G69" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="4">
         <v>1624</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J69" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4760,7 +4838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4789,7 +4867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4818,7 +4896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4847,7 +4925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4876,7 +4954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4905,7 +4983,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4934,7 +5012,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4963,7 +5041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4992,7 +5070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5021,7 +5099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5050,36 +5128,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="G81" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81">
+      <c r="G81" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="4">
         <v>1398</v>
       </c>
-      <c r="I81" t="s">
+      <c r="I81" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5108,7 +5189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5137,7 +5218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5166,7 +5247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5195,7 +5276,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5224,7 +5305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5250,7 +5331,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5279,7 +5360,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5308,7 +5389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5337,7 +5418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5366,7 +5447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5395,7 +5476,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5424,7 +5505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5453,7 +5534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5482,7 +5563,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5511,7 +5592,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5540,7 +5621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5569,7 +5650,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5598,7 +5679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5627,7 +5708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5656,7 +5737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5685,7 +5766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5714,7 +5795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5743,36 +5824,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="G105" t="s">
-        <v>14</v>
-      </c>
-      <c r="H105">
+      <c r="G105" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H105" s="4">
         <v>1255</v>
       </c>
-      <c r="I105" t="s">
+      <c r="I105" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J105" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5801,7 +5885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5830,7 +5914,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5859,7 +5943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5888,7 +5972,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5917,7 +6001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5946,36 +6030,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" s="4">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="G112" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112">
+      <c r="G112" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H112" s="4">
         <v>1831</v>
       </c>
-      <c r="I112" t="s">
+      <c r="I112" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J112" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6004,7 +6091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6033,7 +6120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6062,7 +6149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6091,7 +6178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6120,7 +6207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6149,36 +6236,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="G119" t="s">
-        <v>14</v>
-      </c>
-      <c r="H119">
+      <c r="G119" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H119" s="4">
         <v>7440</v>
       </c>
-      <c r="I119" t="s">
+      <c r="I119" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J119" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6207,7 +6297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6236,7 +6326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6265,7 +6355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6294,7 +6384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6323,7 +6413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6352,7 +6442,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6381,65 +6471,71 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F127" t="s">
+      <c r="F127" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="G127" t="s">
-        <v>14</v>
-      </c>
-      <c r="H127">
+      <c r="G127" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H127" s="4">
         <v>1390</v>
       </c>
-      <c r="I127" t="s">
+      <c r="I127" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128">
+      <c r="J127" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" s="4">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F128" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="G128" t="s">
-        <v>14</v>
-      </c>
-      <c r="H128">
+      <c r="G128" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H128" s="4">
         <v>1114</v>
       </c>
-      <c r="I128" t="s">
+      <c r="I128" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J128" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6468,7 +6564,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6497,7 +6593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6526,7 +6622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6555,7 +6651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6581,7 +6677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6610,7 +6706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6639,7 +6735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6668,36 +6764,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A137">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="F137" t="s">
+      <c r="F137" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="G137" t="s">
-        <v>14</v>
-      </c>
-      <c r="H137">
+      <c r="G137" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H137" s="4">
         <v>1939</v>
       </c>
-      <c r="I137" t="s">
+      <c r="I137" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J137" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6726,7 +6825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6755,7 +6854,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6784,7 +6883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6813,7 +6912,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6842,7 +6941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6871,7 +6970,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6900,7 +6999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6929,7 +7028,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6958,7 +7057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6988,35 +7087,38 @@
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A148">
+      <c r="A148" s="4">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F148" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="G148" t="s">
-        <v>14</v>
-      </c>
-      <c r="H148">
+      <c r="G148" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H148" s="4">
         <v>957</v>
       </c>
-      <c r="I148" t="s">
+      <c r="I148" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J148" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7045,7 +7147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7074,7 +7176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7103,7 +7205,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7132,7 +7234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7162,35 +7264,38 @@
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A154">
+      <c r="A154" s="4">
         <v>153</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F154" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="G154" t="s">
-        <v>14</v>
-      </c>
-      <c r="H154">
+      <c r="G154" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H154" s="4">
         <v>1185</v>
       </c>
-      <c r="I154" t="s">
+      <c r="I154" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J154" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7219,7 +7324,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7248,7 +7353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7277,7 +7382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7306,7 +7411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7335,50 +7440,142 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="4">
+    <row r="160" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="3">
         <v>159</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="D160" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="E160" s="4" t="s">
+      <c r="E160" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="F160" s="4"/>
-      <c r="G160" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H160" s="4">
+      <c r="F160" s="3"/>
+      <c r="G160" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H160" s="3">
         <v>1825</v>
       </c>
-      <c r="I160" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J160" s="4" t="s">
+      <c r="I160" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J160" s="3" t="s">
         <v>752</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J160" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}"/>
+  <autoFilter ref="A1:J160" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Microsoft 365 Business Basic (no Teams)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{EA8A47DA-5E75-4647-879D-B98C23F16FB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22829FDD-79DF-48F8-AE57-654453DB04ED}">
-  <dimension ref="A1"/>
+  <dimension ref="A10:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>528</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>1028</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1110</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>1808</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>1738</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>1823</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>1765</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>7941</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>766</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/OSP O365 License .xlsx
+++ b/OSP O365 License .xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\SLTSERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74726D33-F4C5-417C-9F86-4A1DC5CC736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28976CB-0B06-4264-8852-48C985EBF0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{28F35E17-5A2C-4D9D-B5AC-2CE17E7AC0E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28F35E17-5A2C-4D9D-B5AC-2CE17E7AC0E7}"/>
   </bookViews>
   <sheets>
-    <sheet name="365" sheetId="1" r:id="rId1"/>
-    <sheet name="CAD" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" r:id="rId1"/>
+    <sheet name="365" sheetId="1" r:id="rId2"/>
+    <sheet name="CAD" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'365'!$A$1:$J$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'365'!$A$1:$K$161</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="777">
   <si>
     <t>No</t>
   </si>
@@ -2340,17 +2341,47 @@
     <t>D.K.N.B Delgahapela</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>R.W.M.P.G.M.R. Rajapaksha</t>
+  </si>
+  <si>
+    <t>Before</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
+    <t>Requirment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New </t>
+  </si>
+  <si>
+    <t>Keep 10 Microsoft 365 Business Basic (no Teams) licenses temporarily. Upgrade the remaining 15 current users to Microsoft 365 Business Standard (no Teams).</t>
+  </si>
+  <si>
+    <t>HKQA@slts.lk</t>
+  </si>
+  <si>
+    <t>NEW Mr Venura</t>
+  </si>
+  <si>
+    <t>Mr. Gayan</t>
+  </si>
+  <si>
+    <t>Havlock</t>
+  </si>
+  <si>
+    <t>Qulity Officer</t>
+  </si>
+  <si>
+    <t>New Licenses</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2381,8 +2412,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF424242"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2407,8 +2444,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2416,23 +2459,136 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D1D1"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D1D1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D1D1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D1D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2768,9 +2924,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1806C1D0-1906-47BA-8D5F-6B12DBBCD947}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>766</v>
+      </c>
+      <c r="C1" t="s">
+        <v>767</v>
+      </c>
+      <c r="D1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>133</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>770</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
@@ -2783,42 +3012,45 @@
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="5"/>
+    <col min="11" max="11" width="36.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="6" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2846,8 +3078,11 @@
       <c r="I2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2878,8 +3113,11 @@
       <c r="J3" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2907,8 +3145,11 @@
       <c r="I4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2940,7 +3181,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="6" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2965,8 +3206,11 @@
       <c r="I6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2994,8 +3238,11 @@
       <c r="I7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3023,8 +3270,11 @@
       <c r="I8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3052,8 +3302,11 @@
       <c r="I9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3081,8 +3334,11 @@
       <c r="I10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3110,8 +3366,11 @@
       <c r="I11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3139,8 +3398,11 @@
       <c r="I12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3168,8 +3430,11 @@
       <c r="I13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3197,8 +3462,11 @@
       <c r="I14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3226,8 +3494,11 @@
       <c r="I15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3255,8 +3526,11 @@
       <c r="I16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3284,8 +3558,11 @@
       <c r="I17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3313,8 +3590,11 @@
       <c r="I18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3342,8 +3622,11 @@
       <c r="I19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3371,8 +3654,11 @@
       <c r="I20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3400,8 +3686,11 @@
       <c r="I21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3429,8 +3718,11 @@
       <c r="I22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3458,8 +3750,11 @@
       <c r="I23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3487,8 +3782,11 @@
       <c r="I24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3516,8 +3814,11 @@
       <c r="I25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3545,8 +3846,11 @@
       <c r="I26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3575,8 +3879,11 @@
       <c r="J27" s="3" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3604,8 +3911,11 @@
       <c r="I28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3633,8 +3943,11 @@
       <c r="I29" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3662,8 +3975,11 @@
       <c r="I30" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3691,8 +4007,11 @@
       <c r="I31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -3723,8 +4042,11 @@
       <c r="J32" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3752,8 +4074,11 @@
       <c r="I33" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3781,8 +4106,11 @@
       <c r="I34" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3810,8 +4138,11 @@
       <c r="I35" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3839,8 +4170,11 @@
       <c r="I36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3868,8 +4202,11 @@
       <c r="I37" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3897,8 +4234,11 @@
       <c r="I38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3926,8 +4266,11 @@
       <c r="I39" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3955,37 +4298,46 @@
       <c r="I40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="K40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="7">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41">
+      <c r="G41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="7">
         <v>531</v>
       </c>
-      <c r="I41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="K41" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4013,8 +4365,11 @@
       <c r="I42" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4042,8 +4397,11 @@
       <c r="I43" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -4074,8 +4432,11 @@
       <c r="J44" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4103,8 +4464,11 @@
       <c r="I45" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4132,8 +4496,11 @@
       <c r="I46" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4158,8 +4525,11 @@
       <c r="I47" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4187,8 +4557,11 @@
       <c r="I48" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4216,8 +4589,11 @@
       <c r="I49" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K49" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4245,8 +4621,11 @@
       <c r="I50" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4274,8 +4653,11 @@
       <c r="I51" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4303,8 +4685,11 @@
       <c r="I52" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4332,8 +4717,11 @@
       <c r="I53" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4361,8 +4749,11 @@
       <c r="I54" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4390,8 +4781,11 @@
       <c r="I55" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K55" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4419,8 +4813,11 @@
       <c r="I56" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K56" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4448,8 +4845,11 @@
       <c r="I57" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4477,8 +4877,11 @@
       <c r="I58" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K58" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4506,8 +4909,11 @@
       <c r="I59" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K59" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4535,8 +4941,11 @@
       <c r="I60" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4567,8 +4976,11 @@
       <c r="J61" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K61" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4596,8 +5008,11 @@
       <c r="I62" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -4628,8 +5043,11 @@
       <c r="J63" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4657,8 +5075,11 @@
       <c r="I64" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -4690,7 +5111,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="66" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4718,8 +5139,11 @@
       <c r="I66" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4747,8 +5171,11 @@
       <c r="I67" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4776,8 +5203,11 @@
       <c r="I68" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -4808,8 +5238,11 @@
       <c r="J69" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4837,8 +5270,11 @@
       <c r="I70" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4866,8 +5302,11 @@
       <c r="I71" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4895,8 +5334,11 @@
       <c r="I72" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4924,8 +5366,11 @@
       <c r="I73" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4953,8 +5398,11 @@
       <c r="I74" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4982,8 +5430,11 @@
       <c r="I75" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K75" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5011,8 +5462,11 @@
       <c r="I76" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5040,8 +5494,11 @@
       <c r="I77" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5069,8 +5526,11 @@
       <c r="I78" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K78" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5098,8 +5558,11 @@
       <c r="I79" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K79" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5127,8 +5590,11 @@
       <c r="I80" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -5159,8 +5625,11 @@
       <c r="J81" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5188,8 +5657,11 @@
       <c r="I82" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5217,8 +5689,11 @@
       <c r="I83" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5246,8 +5721,11 @@
       <c r="I84" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5275,8 +5753,11 @@
       <c r="I85" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5304,8 +5785,11 @@
       <c r="I86" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K86" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5330,8 +5814,11 @@
       <c r="I87" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K87" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5359,8 +5846,11 @@
       <c r="I88" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K88" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5388,8 +5878,11 @@
       <c r="I89" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K89" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5417,8 +5910,11 @@
       <c r="I90" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K90" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5446,8 +5942,11 @@
       <c r="I91" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K91" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5475,8 +5974,11 @@
       <c r="I92" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K92" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5504,8 +6006,11 @@
       <c r="I93" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K93" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5533,8 +6038,11 @@
       <c r="I94" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K94" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5562,8 +6070,11 @@
       <c r="I95" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K95" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5591,8 +6102,11 @@
       <c r="I96" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K96" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5620,8 +6134,11 @@
       <c r="I97" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K97" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5649,8 +6166,11 @@
       <c r="I98" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K98" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5678,8 +6198,11 @@
       <c r="I99" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K99" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5707,8 +6230,11 @@
       <c r="I100" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K100" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5736,8 +6262,11 @@
       <c r="I101" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K101" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5765,8 +6294,11 @@
       <c r="I102" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K102" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5794,8 +6326,11 @@
       <c r="I103" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K103" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5823,8 +6358,11 @@
       <c r="I104" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K104" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -5855,8 +6393,11 @@
       <c r="J105" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K105" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5884,8 +6425,11 @@
       <c r="I106" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K106" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5913,8 +6457,11 @@
       <c r="I107" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K107" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5942,8 +6489,11 @@
       <c r="I108" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K108" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5971,8 +6521,11 @@
       <c r="I109" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K109" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6000,8 +6553,11 @@
       <c r="I110" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K110" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6029,8 +6585,11 @@
       <c r="I111" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K111" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -6061,8 +6620,11 @@
       <c r="J112" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K112" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6090,8 +6652,11 @@
       <c r="I113" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K113" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6119,8 +6684,11 @@
       <c r="I114" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6148,8 +6716,11 @@
       <c r="I115" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K115" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6177,8 +6748,11 @@
       <c r="I116" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K116" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6206,8 +6780,11 @@
       <c r="I117" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K117" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6235,8 +6812,11 @@
       <c r="I118" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K118" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -6267,8 +6847,11 @@
       <c r="J119" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K119" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6296,8 +6879,11 @@
       <c r="I120" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K120" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6325,8 +6911,11 @@
       <c r="I121" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K121" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6354,8 +6943,11 @@
       <c r="I122" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K122" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6383,8 +6975,11 @@
       <c r="I123" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K123" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6412,8 +7007,11 @@
       <c r="I124" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K124" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6441,8 +7039,11 @@
       <c r="I125" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K125" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6470,8 +7071,11 @@
       <c r="I126" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K126" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -6502,8 +7106,11 @@
       <c r="J127" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K127" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -6534,8 +7141,11 @@
       <c r="J128" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K128" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6563,8 +7173,11 @@
       <c r="I129" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K129" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6592,8 +7205,11 @@
       <c r="I130" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6621,8 +7237,11 @@
       <c r="I131" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K131" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6650,8 +7269,11 @@
       <c r="I132" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K132" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6676,8 +7298,11 @@
       <c r="I133" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K133" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6705,8 +7330,11 @@
       <c r="I134" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K134" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6734,8 +7362,11 @@
       <c r="I135" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K135" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6763,8 +7394,11 @@
       <c r="I136" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K136" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -6795,8 +7429,11 @@
       <c r="J137" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K137" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6824,8 +7461,11 @@
       <c r="I138" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K138" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6853,8 +7493,11 @@
       <c r="I139" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K139" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6882,8 +7525,11 @@
       <c r="I140" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K140" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6911,8 +7557,11 @@
       <c r="I141" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K141" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6940,8 +7589,11 @@
       <c r="I142" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K142" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6969,8 +7621,11 @@
       <c r="I143" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K143" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6998,8 +7653,11 @@
       <c r="I144" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K144" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7027,8 +7685,11 @@
       <c r="I145" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K145" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7056,8 +7717,11 @@
       <c r="I146" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K146" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7085,8 +7749,11 @@
       <c r="I147" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K147" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -7117,8 +7784,11 @@
       <c r="J148" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K148" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7146,8 +7816,11 @@
       <c r="I149" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K149" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7175,8 +7848,11 @@
       <c r="I150" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K150" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7204,8 +7880,11 @@
       <c r="I151" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K151" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7233,8 +7912,11 @@
       <c r="I152" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K152" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7262,8 +7944,11 @@
       <c r="I153" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K153" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -7294,8 +7979,11 @@
       <c r="J154" s="4" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K154" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7323,8 +8011,11 @@
       <c r="I155" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K155" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7352,8 +8043,11 @@
       <c r="I156" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K156" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7381,8 +8075,11 @@
       <c r="I157" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K157" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7410,8 +8107,11 @@
       <c r="I158" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K158" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7439,8 +8139,11 @@
       <c r="I159" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K159" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -7469,15 +8172,41 @@
       <c r="J160" s="3" t="s">
         <v>752</v>
       </c>
+      <c r="K160" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A161" s="3">
+        <v>160</v>
+      </c>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="K161" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J160" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="Microsoft 365 Business Basic (no Teams)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K161" xr:uid="{D93E8B5A-7983-4C4C-8219-9B8F766801AA}"/>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{EA8A47DA-5E75-4647-879D-B98C23F16FB5}"/>
   </hyperlinks>
@@ -7486,96 +8215,121 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22829FDD-79DF-48F8-AE57-654453DB04ED}">
-  <dimension ref="A10:B19"/>
+  <dimension ref="A10:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
     <col min="2" max="2" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="C10" s="11" t="s">
+        <v>773</v>
+      </c>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
         <v>528</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="C11" s="13"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
         <v>1028</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
         <v>1110</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="C13" s="13"/>
+      <c r="D13" s="14"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
         <v>1808</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
         <v>1738</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
         <v>1823</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
         <v>1765</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+      <c r="C17" s="13"/>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
         <v>7941</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>765</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>766</v>
-      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C10:D19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>